--- a/math_expression_generator/result/metals4u.co_output.xlsx
+++ b/math_expression_generator/result/metals4u.co_output.xlsx
@@ -658,25 +658,15 @@
           <t>screenshots\metals4u.co\https_www.metals4u.co.uk_shop-by-application_building-construction_concrete-reinforcement_rebar_7552.png</t>
         </is>
       </c>
-      <c r="Z2" t="n">
-        <v>1019064.935064935</v>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>price * (1000 / 3.85)</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Convert £/m to £/t using weight per metre 3.85 kg: 1 m costs price and weighs 3.85 kg, so 1000 kg (1 t) corresponds to (1000/3.85) metres.</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>SCREENSHOT</t>
-        </is>
-      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>FATAL_ERROR: cannot access local variable 'response' where it is not associated with a value</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -760,25 +750,15 @@
           <t>screenshots\metals4u.co\https_www.metals4u.co.uk_shop-by-application_building-construction_concrete-reinforcement_rebar_7550.png</t>
         </is>
       </c>
-      <c r="Z3" t="n">
-        <v>1287036.437246963</v>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>price * (1000 / 2.47)</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Convert £/m to £/t using weight per metre: 2.47 kg per metre. 1 t = 1000 kg, so metres per tonne = 1000/2.47; multiply the per-metre price by this factor to get per-tonne price.</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>SCREENSHOT</t>
-        </is>
-      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>FATAL_ERROR: cannot access local variable 'response' where it is not associated with a value</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -862,25 +842,15 @@
           <t>screenshots\metals4u.co\https_www.metals4u.co.uk_shop-by-application_building-construction_concrete-reinforcement_rebar_7548.png</t>
         </is>
       </c>
-      <c r="Z4" t="n">
-        <v>1986265.82278481</v>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>price*(1000/1.58)</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Convert £/m to £/t using weight per metre: 1.58 kg per metre, so metres per tonne = 1000/1.58. Multiply price per metre by metres per tonne to get price per tonne.</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>SCREENSHOT</t>
-        </is>
-      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>FATAL_ERROR: cannot access local variable 'response' where it is not associated with a value</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -964,25 +934,15 @@
           <t>screenshots\metals4u.co\https_www.metals4u.co.uk_shop-by-application_building-construction_concrete-reinforcement_rebar_7547.png</t>
         </is>
       </c>
-      <c r="Z5" t="n">
-        <v>3997932.584269663</v>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>price*(1000/0.89)</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Convert £/m to £/t using weight per metre (0.89 kg per metre): £/t = (£/m) * (metres per tonne) = price * (1000 kg / 0.89 kg per m).</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>SCREENSHOT</t>
-        </is>
-      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>FATAL_ERROR: cannot access local variable 'response' where it is not associated with a value</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1066,25 +1026,15 @@
           <t>screenshots\metals4u.co\https_www.metals4u.co.uk_shop-by-application_building-construction_concrete-reinforcement_rebar_7549.png</t>
         </is>
       </c>
-      <c r="Z6" t="n">
-        <v>6522193.548387097</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>price*(1000/0.62)</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Convert £/m to £/t using weight per metre (0.62 kg per metre) and 1000 kg per tonne.</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>SCREENSHOT</t>
-        </is>
-      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>FATAL_ERROR: cannot access local variable 'response' where it is not associated with a value</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
